--- a/data/metadata/Informe-01-010055-A-TC-TM-TP.xlsx
+++ b/data/metadata/Informe-01-010055-A-TC-TM-TP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riamlab-my.sharepoint.com/personal/fernandomartinez_gnoss_com/Documents/Proyectos/AOD/Repositorios/local-data-aragopedia/data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_CE18C25D4BD36059694D7F25444F80EF0E4A5A30" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9AAB2EA-2F91-4DF6-962A-A4096BE6271E}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="11_CE18C25D4BD36059694D7F25444F80EF0E4A5A30" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0783386D-686A-4381-BAF2-EDA086C43508}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="8280" windowWidth="30045" windowHeight="8220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informe-05-050314-A-TC-TP" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
   <si>
     <t>sdmx-dimension:refArea</t>
   </si>
@@ -252,52 +252,58 @@
     <t>iaest-measure:personas-mano-obra-familiar-conyuges-que-trabajan-en-otra-actividad-como-secundaria</t>
   </si>
   <si>
-    <t>personas-mano-obra-familiar-otros-que- trabajan-tambien-en-otra-activ-lucrativa</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-otros-que- trabajan-tambien-en-otra-activ-lucrativa</t>
-  </si>
-  <si>
-    <t>personas-mano-obra-familiar-otros-trabajan-en-otra-actividad-como-principal</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-otros-trabajan-en-otra-actividad-como-principal</t>
-  </si>
-  <si>
     <t>personas-mano-obra-familiar-otros-que-trabajan-en-otra-actividad-como-secundaria</t>
   </si>
   <si>
     <t>iaest-measure:personas-mano-obra-familiar-otros-que-trabajan-en-otra-actividad-como-secundaria</t>
   </si>
   <si>
-    <t>personas-mano-obra-familiar-con-25-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-con-25-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>personas-mano-obra-familiar-con-24-99-y-50-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-con-24-99-y-50-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>personas-mano-obra-familiar-con-49-99-y-75-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-con-49-99-y-75-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>personas-mano-obra-familiar-con-74-99-y-100-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-con-74-99-y-100-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>personas-mano-obra-familiar-con-100-trabajando-en-explotacion</t>
-  </si>
-  <si>
-    <t>iaest-measure:personas-mano-obra-familiar-con-100-trabajando-en-explotacion</t>
+    <t>personas-mano-obra-familiar-con-100porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-con-100porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-con-7499-y-100porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-con-7499-y-100porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-con-4999-y-75porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-con-4999-y-75porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-con-2499-y-50porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-con-2499-y-50porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-con-25porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-con-25porcentaje-trabajando-en-explotacion</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-otros--trabajan-en-otra-actividad-como-principal</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-otros--trabajan-en-otra-actividad-como-principal</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-otros-que--trabajan-tambien-en-otra-activ-lucrativa</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-otros-que--trabajan-tambien-en-otra-activ-lucrativa</t>
+  </si>
+  <si>
+    <t>personas-mano-obra-familiar-otros-que-solo-trabajan-en-la-explotacion</t>
+  </si>
+  <si>
+    <t>iaest-measure:personas-mano-obra-familiar-otros-que-solo-trabajan-en-la-explotacion</t>
   </si>
 </sst>
 </file>
@@ -844,31 +850,31 @@
         <v>73</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="W2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="Z2" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>83</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
@@ -936,31 +942,31 @@
         <v>74</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="W3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="X3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="Z3" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AA3" s="3" t="s">
         <v>84</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
